--- a/pdf2img/hasil_ekstraksi/table_5/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_5/tabel_1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LAPORAN PLRDITUNGAN KIWAIBAN PITIOLAAN MOOAL MILNUM KPHUND Pet 31 Detembet 202s dan 2024</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KCMPOOEN MODAL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31-00-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31.00s-24</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Modal irt ( Ter 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1 Modal inti Utama / Common Equly Ter 1 (CET 1)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13.290624 13290.624</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12.409722 12.499.722</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11 Modal Cietor (Seen daurangl Treury Stock) 12Catangon Tambahan Modal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1338 539 11.952.005</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.8539 11341.183 15.601 457</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>121 Fanaor Peruamtan 1211 Pendacta kprehn lan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seinn ecrar ipra ag</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Seinn ecrar ipra ag</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Seinn ecrar ipra ag</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15.697 702 1567 798</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1538948</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12111 12112</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>65.729</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12113 Sano turpiun rauan anet etng Caarngan uarbanan mon larryo (oer lhcicaed rderea)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1 502. 009</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12121 Agio</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14 129.904 8354 829</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14 002.519</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12.12.2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Carangan urum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>132.600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8.364 829 131600</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Laca arur-tarun ate</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.457 988 29.975</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3.396.001</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12124</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Laca aun beranan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2 164 56</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12.12.5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dara wotorar modal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2. 1668 516</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1212.6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lanryg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0745417)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F akior Pengurang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(4 240 284)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pencnaar kopre lany Sg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(20 602)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12212</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0745617</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(20.602)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Catanpun urtanan moda lairrya (cher ficioted monea)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(4219.682)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12221 Ditagio</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fagj arup carue lal.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12222 12223</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pogi arun beraan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>(0587 669)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12226</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Se ng ara Peuan Pngaun Ka Adel (ppKA) a Caaa Kerga Perura Ma CXP an aet pr 12225</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SegTrn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>(57918)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>(4.037 482)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1222.6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pPA prdf</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>(1*2.200)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12221 .a的ry物</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Keptntingn Moa Peagendall ying dnpun deerhiturg an</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14 1.4.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fator Penguring Modal ins Ueams Ptrhnrgan gpa argyuhan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Goodteil</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aut ioaa beratpud laney</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ptnyeraa ang inga aga har pengurag</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14.4 14.5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kragp</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14馬</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Exasgpour ten,rBha</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Facr pengurang moca in taa lanny</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Panegaan Cara pa rnumen AT 1 aina Ter 2 paa bart an</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kecedban slang saa ennan lan yang dlgern beamanan perairar arra Pum, htat afa, iba mnn</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2 Modal linti Tamtahani Ascitonal Tier (AT )</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ruuen yang memenui peryarn AT1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>22 Agio Oiuagio</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fator Pergurarg Mocal nt Tamtaram</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>23 211</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Panergaan Gaa sacs rnrumnn AI 1 canlaau T</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ther 2 pada bure an</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>644.721</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>794.806</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Modal Pehengao (Tier Z)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1 Inatrumtn modal dalam benbuk sahum stau lainrya ying memerund port yarstan Tier ?</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10.409</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2 Agio / dhagio</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3 Caangan umum PprA stan st predagl yang wejb ditonuk (palng tnggi 1 2%, ATma Rhiho Kredr)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>64.721</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>491.107</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4 Fakcor Pengurng Modal Peitngp ao</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4.1 Sineing Funs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42 Pnepa p Ter 2paa a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tets Modal</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>11979 345</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13.496 528</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KETERANGAN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>11.0024 11.01-24</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KETERANGAN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>11.008</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>11.00024</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SET TERTIMBANG MENURUT RISKO</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RASIO KOMM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AIMR RUSKO KREDIT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>134 230 605 125106.008</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ro CET 1 (%)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AMR RUSKO PASAR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>auo Taer 1 (%)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>&amp;*11581</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AIMR RUSKO OPERASIOPAL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.410.612</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Rao Taer 2 (%)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10. 10%</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TOTAL ATMR</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>134 101878</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>128.597 28sRnio KOPmm (%)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10.50%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1082% CET 1 UNTUK BUFER (%)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SO KOPWM SESUAJ PROFL, RSIKO (%)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>.1%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2,500% 0.000% 0000</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.800% 0.000% 0.000%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dari CET 1 (%) Dari AT 1 (%) Darl Ther 2 (%)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OKASI PEMEUPLAN KPIIM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10.12% 0.00% 0.50h</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PERSENTASE BUFFER YANG WAJIB CIPENUPI OLEPH BANK 10 20% Capiad Comervtion Buler (%4) 0.00l Ccunare yrhcal Bufer (%) 0.62yCapital Surcharge</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf2img/hasil_ekstraksi/table_5/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_5/tabel_1.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_extraction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cleaned_output" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,21 +29,15 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-        <bgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,34 +51,14 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,772 +427,702 @@
   </sheetPr>
   <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="3" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>M B B</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>B C Ma E Po :</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr"/>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr"/>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr"/>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
-      <c r="B31" s="3" t="inlineStr"/>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr"/>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr"/>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
-      <c r="B35" s="3" t="inlineStr"/>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
-      <c r="B36" s="3" t="inlineStr"/>
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr"/>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr"/>
-      <c r="B38" s="3" t="inlineStr"/>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="3" t="inlineStr"/>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
-      <c r="B40" s="3" t="inlineStr"/>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
-      <c r="B41" s="3" t="inlineStr"/>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
-      <c r="B42" s="3" t="inlineStr"/>
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
-      <c r="B43" s="3" t="inlineStr"/>
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr"/>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
-      <c r="B45" s="3" t="inlineStr"/>
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr"/>
-      <c r="B46" s="3" t="inlineStr"/>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="3" t="inlineStr"/>
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr"/>
-      <c r="B50" s="3" t="inlineStr"/>
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
-      <c r="B51" s="3" t="inlineStr"/>
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr"/>
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr"/>
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr"/>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr"/>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
-      <c r="B56" s="3" t="inlineStr"/>
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr"/>
-      <c r="B57" s="3" t="inlineStr"/>
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
-      <c r="B58" s="3" t="inlineStr"/>
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr"/>
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr"/>
-      <c r="B60" s="3" t="inlineStr"/>
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr"/>
-      <c r="B61" s="3" t="inlineStr"/>
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr"/>
-      <c r="B62" s="3" t="inlineStr"/>
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr"/>
-      <c r="B63" s="3" t="inlineStr"/>
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
-      <c r="B64" s="3" t="inlineStr"/>
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr"/>
-      <c r="B65" s="3" t="inlineStr"/>
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr"/>
-      <c r="B66" s="3" t="inlineStr"/>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr"/>
-      <c r="B67" s="3" t="inlineStr"/>
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr"/>
-      <c r="B68" s="3" t="inlineStr"/>
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr"/>
-      <c r="B69" s="3" t="inlineStr"/>
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr"/>
-      <c r="B70" s="3" t="inlineStr"/>
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr"/>
-      <c r="B71" s="3" t="inlineStr"/>
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
-      <c r="B72" s="3" t="inlineStr"/>
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="3" t="inlineStr"/>
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
-      <c r="B74" s="3" t="inlineStr"/>
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr"/>
-      <c r="B75" s="3" t="inlineStr"/>
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr"/>
-      <c r="B76" s="3" t="inlineStr"/>
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr"/>
-      <c r="B77" s="3" t="inlineStr"/>
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr"/>
-      <c r="B78" s="3" t="inlineStr"/>
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr"/>
-      <c r="B79" s="3" t="inlineStr"/>
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr"/>
-      <c r="B80" s="3" t="inlineStr"/>
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
-      <c r="B81" s="3" t="inlineStr"/>
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr"/>
-      <c r="B82" s="3" t="inlineStr"/>
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr"/>
-      <c r="B83" s="3" t="inlineStr"/>
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr"/>
-      <c r="B84" s="3" t="inlineStr"/>
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr"/>
-      <c r="B85" s="3" t="inlineStr"/>
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr"/>
-      <c r="B86" s="3" t="inlineStr"/>
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr"/>
-      <c r="B87" s="3" t="inlineStr"/>
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr"/>
-      <c r="B88" s="3" t="inlineStr"/>
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr"/>
-      <c r="B89" s="3" t="inlineStr"/>
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr"/>
-      <c r="B90" s="3" t="inlineStr"/>
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr"/>
-      <c r="B91" s="3" t="inlineStr"/>
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr"/>
-      <c r="B92" s="3" t="inlineStr"/>
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr"/>
-      <c r="B93" s="3" t="inlineStr"/>
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr"/>
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr"/>
-      <c r="B95" s="3" t="inlineStr"/>
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr"/>
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr"/>
-      <c r="B97" s="3" t="inlineStr"/>
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr"/>
-      <c r="B98" s="3" t="inlineStr"/>
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr"/>
-      <c r="B99" s="3" t="inlineStr"/>
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr"/>
-      <c r="B100" s="3" t="inlineStr"/>
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr"/>
-      <c r="B101" s="3" t="inlineStr"/>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr"/>
-      <c r="B102" s="3" t="inlineStr"/>
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr"/>
-      <c r="B103" s="3" t="inlineStr"/>
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr"/>
-      <c r="B104" s="3" t="inlineStr"/>
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
-      <c r="B105" s="3" t="inlineStr"/>
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr"/>
-      <c r="B106" s="3" t="inlineStr"/>
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr"/>
-      <c r="B107" s="3" t="inlineStr"/>
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr"/>
-      <c r="B108" s="3" t="inlineStr"/>
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr"/>
-      <c r="B109" s="3" t="inlineStr"/>
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr"/>
-      <c r="B110" s="3" t="inlineStr"/>
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr"/>
-      <c r="B111" s="3" t="inlineStr"/>
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr"/>
-      <c r="B112" s="3" t="inlineStr"/>
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr"/>
-      <c r="B113" s="3" t="inlineStr"/>
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr"/>
-      <c r="B114" s="3" t="inlineStr"/>
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr"/>
-      <c r="B115" s="3" t="inlineStr"/>
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr"/>
-      <c r="B116" s="3" t="inlineStr"/>
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr"/>
-      <c r="B117" s="3" t="inlineStr"/>
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr"/>
-      <c r="B118" s="3" t="inlineStr"/>
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr"/>
-      <c r="B119" s="3" t="inlineStr"/>
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr"/>
-      <c r="B120" s="3" t="inlineStr"/>
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr"/>
-      <c r="B121" s="3" t="inlineStr"/>
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr"/>
-      <c r="B122" s="3" t="inlineStr"/>
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr"/>
-      <c r="B123" s="3" t="inlineStr"/>
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr"/>
-      <c r="B124" s="3" t="inlineStr"/>
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr"/>
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr"/>
-      <c r="B126" s="3" t="inlineStr"/>
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr"/>
-      <c r="B127" s="3" t="inlineStr"/>
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr"/>
-      <c r="B128" s="3" t="inlineStr"/>
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr"/>
-      <c r="B129" s="3" t="inlineStr"/>
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
-      <c r="B130" s="3" t="inlineStr"/>
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr"/>
-      <c r="B131" s="3" t="inlineStr"/>
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr"/>
-      <c r="B132" s="3" t="inlineStr"/>
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr"/>
-      <c r="B133" s="3" t="inlineStr"/>
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr"/>
-      <c r="B134" s="3" t="inlineStr"/>
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr"/>
-      <c r="B135" s="3" t="inlineStr"/>
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr"/>
-      <c r="B136" s="3" t="inlineStr"/>
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr"/>
-      <c r="B137" s="3" t="inlineStr"/>
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr"/>
-      <c r="B138" s="3" t="inlineStr"/>
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr"/>
-      <c r="B139" s="3" t="inlineStr"/>
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr"/>
-      <c r="B140" s="3" t="inlineStr"/>
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr"/>
-      <c r="B141" s="3" t="inlineStr"/>
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr"/>
-      <c r="B142" s="3" t="inlineStr"/>
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr"/>
-      <c r="B143" s="3" t="inlineStr"/>
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr"/>
-      <c r="B144" s="3" t="inlineStr"/>
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr"/>
-      <c r="B145" s="3" t="inlineStr"/>
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr"/>
-      <c r="B146" s="3" t="inlineStr"/>
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr"/>
-      <c r="B147" s="3" t="inlineStr"/>
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr"/>
-      <c r="B148" s="3" t="inlineStr"/>
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr"/>
-      <c r="B149" s="3" t="inlineStr"/>
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr"/>
-      <c r="B150" s="3" t="inlineStr"/>
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr"/>
-      <c r="B151" s="3" t="inlineStr"/>
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr"/>
-      <c r="B152" s="3" t="inlineStr"/>
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr"/>
-      <c r="B153" s="3" t="inlineStr"/>
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr"/>
-      <c r="B154" s="3" t="inlineStr"/>
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr"/>
-      <c r="B155" s="3" t="inlineStr"/>
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr"/>
-      <c r="B156" s="3" t="inlineStr"/>
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr"/>
-      <c r="B157" s="3" t="inlineStr"/>
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr"/>
-      <c r="B158" s="3" t="inlineStr"/>
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr"/>
-      <c r="B159" s="3" t="inlineStr"/>
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr"/>
-      <c r="B160" s="3" t="inlineStr"/>
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr"/>
-      <c r="B161" s="3" t="inlineStr"/>
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr"/>
-      <c r="B162" s="3" t="inlineStr"/>
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr"/>
-      <c r="B163" s="3" t="inlineStr"/>
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr"/>
-      <c r="B164" s="3" t="inlineStr"/>
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr"/>
-      <c r="B165" s="3" t="inlineStr"/>
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>2 2 4 5 6 2 1 7 3 12 =</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>M B B</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>B C Ma E Po :</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2 2 4 5 6 2 1 7 3 12 =</t>
-        </is>
-      </c>
+      <c r="B166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
